--- a/tabelas/sit_and_reach2.xlsx
+++ b/tabelas/sit_and_reach2.xlsx
@@ -1,3 +1,140 @@
+
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
+</file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
@@ -280,4 +417,339 @@
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Weigth</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Real distance</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Calculated distance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="G2" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>-24</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-23.51</v>
+      </c>
+      <c r="G3" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="G4" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>-24</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-23.98</v>
+      </c>
+      <c r="G5" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="G6" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="G7" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>-7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-7.51</v>
+      </c>
+      <c r="G8" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>20</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="G9" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>20</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="G10" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>20</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="G11" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>20</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="G12" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/tabelas/sit_and_reach2.xlsx
+++ b/tabelas/sit_and_reach2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -719,15 +719,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
+      <c r="A13" t="n">
+        <v>20</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1.62</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
@@ -738,14 +734,110 @@
       <c r="E13" t="n">
         <v>4</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>3.05</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>54</t>
+      <c r="F13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G13" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>19</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-11.81</v>
+      </c>
+      <c r="G14" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>19</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-2.67</v>
+      </c>
+      <c r="G15" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>19</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="G16" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>-8</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-8.48</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>82</t>
         </is>
       </c>
     </row>

--- a/tabelas/sit_and_reach2.xlsx
+++ b/tabelas/sit_and_reach2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -811,15 +811,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
+      <c r="A17" t="n">
+        <v>19</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1.74</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
@@ -830,12 +826,108 @@
       <c r="E17" t="n">
         <v>-8</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>-8.48</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F17" t="n">
+        <v>-8.48</v>
+      </c>
+      <c r="G17" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>19</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="G18" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>19</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G19" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>-32</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-32.91</v>
+      </c>
+      <c r="G20" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>-18</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-18.09</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>82</t>
         </is>

--- a/tabelas/sit_and_reach2.xlsx
+++ b/tabelas/sit_and_reach2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,15 +903,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1.74</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
@@ -922,14 +918,110 @@
       <c r="E21" t="n">
         <v>-18</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>-18.09</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>82</t>
+      <c r="F21" t="n">
+        <v>-18.09</v>
+      </c>
+      <c r="G21" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="G22" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-3.21</v>
+      </c>
+      <c r="G23" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-4.38</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>-15</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-14.86</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/tabelas/sit_and_reach2.xlsx
+++ b/tabelas/sit_and_reach2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -972,15 +972,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
+      <c r="A24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1.74</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
@@ -991,14 +987,110 @@
       <c r="E24" t="n">
         <v>-16</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-17.00</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>82</t>
+      <c r="F24" t="n">
+        <v>-17</v>
+      </c>
+      <c r="G24" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-13.26</v>
+      </c>
+      <c r="G25" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>20</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>-15.8</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-16.75</v>
+      </c>
+      <c r="G26" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>20</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>-16</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-16.44</v>
+      </c>
+      <c r="G27" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>-14.2</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-15.01</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>52</t>
         </is>
       </c>
     </row>

--- a/tabelas/sit_and_reach2.xlsx
+++ b/tabelas/sit_and_reach2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1064,15 +1064,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
+      <c r="A28" t="n">
+        <v>20</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1.64</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
@@ -1083,12 +1079,108 @@
       <c r="E28" t="n">
         <v>-14.2</v>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>-15.01</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="F28" t="n">
+        <v>-15.01</v>
+      </c>
+      <c r="G28" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>20</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>-9</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-9.380000000000001</v>
+      </c>
+      <c r="G29" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>20</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="G30" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>20</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>-11</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-11.47</v>
+      </c>
+      <c r="G31" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Feminine</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>-7</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-7.51</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>52</t>
         </is>

--- a/tabelas/sit_and_reach2.xlsx
+++ b/tabelas/sit_and_reach2.xlsx
@@ -1,37 +1,95 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Propicie\tabelas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41281DE6-D07D-403F-A5EF-84D3BDE9BE34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="11">
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Height</t>
+  </si>
+  <si>
+    <t>Weigth</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Real distance</t>
+  </si>
+  <si>
+    <t>Calculated distance</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Feminine</t>
+  </si>
+  <si>
+    <t>-6.40</t>
+  </si>
+  <si>
+    <t>Erro</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +104,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,770 +428,970 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Age</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Height</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Weigth</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Gender</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Real distance</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Calculated distance</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Weight</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2">
         <v>19</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>1.74</v>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>-0.62</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
+        <f>ABS(ABS(E2)-ABS(F2))</f>
+        <v>0.62</v>
+      </c>
+      <c r="H2">
         <v>82</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>19</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>1.74</v>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3">
         <v>-24</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>-23.51</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
+        <f t="shared" ref="G3:G40" si="0">ABS(ABS(E3)-ABS(F3))</f>
+        <v>0.48999999999999844</v>
+      </c>
+      <c r="H3">
         <v>82</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
         <v>19</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>1.74</v>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4">
         <v>6</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>6.26</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>0.25999999999999979</v>
+      </c>
+      <c r="H4">
         <v>82</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
         <v>19</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>1.74</v>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5">
         <v>-24</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>-23.98</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>1.9999999999999574E-2</v>
+      </c>
+      <c r="H5">
         <v>82</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>20</v>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>20</v>
+      </c>
+      <c r="B6">
         <v>1.62</v>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Feminine</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6">
         <v>4</v>
       </c>
-      <c r="F6" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="F6">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>0.26999999999999957</v>
+      </c>
+      <c r="H6">
         <v>52</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>20</v>
+      </c>
+      <c r="B7">
         <v>1.62</v>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Feminine</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7">
         <v>5.8</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>5.73</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>6.9999999999999396E-2</v>
+      </c>
+      <c r="H7">
         <v>52</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>20</v>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>20</v>
+      </c>
+      <c r="B8">
         <v>1.62</v>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Feminine</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8">
         <v>-7</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>-7.51</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>0.50999999999999979</v>
+      </c>
+      <c r="H8">
         <v>52</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>20</v>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>20</v>
+      </c>
+      <c r="B9">
         <v>1.62</v>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Feminine</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9">
         <v>-4</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>-4.16</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>0.16000000000000014</v>
+      </c>
+      <c r="H9">
         <v>52</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>20</v>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>20</v>
+      </c>
+      <c r="B10">
         <v>1.62</v>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Feminine</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10" t="n">
-        <v>-1.15</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="F10">
+        <v>-1.1499999999999999</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="H10">
         <v>52</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>20</v>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>20</v>
+      </c>
+      <c r="B11">
         <v>1.62</v>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Feminine</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>-1.28</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>1.28</v>
+      </c>
+      <c r="H11">
         <v>52</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>20</v>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>20</v>
+      </c>
+      <c r="B12">
         <v>1.62</v>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Feminine</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
+      <c r="D12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12">
         <v>2.4</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>2.35</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>4.9999999999999822E-2</v>
+      </c>
+      <c r="H12">
         <v>54</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>20</v>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>20</v>
+      </c>
+      <c r="B13">
         <v>1.62</v>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Feminine</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
+      <c r="D13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13">
         <v>4</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>3.05</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>0.95000000000000018</v>
+      </c>
+      <c r="H13">
         <v>54</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14">
         <v>19</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>1.74</v>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
+      <c r="D14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14">
         <v>11.5</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>-11.81</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>0.3100000000000005</v>
+      </c>
+      <c r="H14">
         <v>82</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15">
         <v>19</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>1.74</v>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
+      <c r="D15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15">
         <v>-2.4</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>-2.67</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>0.27</v>
+      </c>
+      <c r="H15">
         <v>82</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16">
         <v>19</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>1.74</v>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
+      <c r="D16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16">
         <v>-4</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>3.36</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>0.64000000000000012</v>
+      </c>
+      <c r="H16">
         <v>82</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17">
         <v>19</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>1.74</v>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17">
         <v>-8</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>-8.48</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>0.48000000000000043</v>
+      </c>
+      <c r="H17">
         <v>82</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18">
         <v>19</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>1.74</v>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
+      <c r="D18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18">
         <v>0</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>-1.66</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>1.66</v>
+      </c>
+      <c r="H18">
         <v>82</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19">
         <v>19</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>1.74</v>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
+      <c r="D19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19">
         <v>4.8</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>4.7</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999645E-2</v>
+      </c>
+      <c r="H19">
         <v>82</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>1.74</v>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
+      <c r="D20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20">
         <v>-32</v>
       </c>
-      <c r="F20" t="n">
-        <v>-32.91</v>
-      </c>
-      <c r="G20" t="n">
+      <c r="F20">
+        <v>-32.909999999999997</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="0"/>
+        <v>0.90999999999999659</v>
+      </c>
+      <c r="H20">
         <v>82</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21">
         <v>19</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>1.74</v>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
+      <c r="D21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21">
         <v>-18</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>-18.09</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21">
+        <f t="shared" si="0"/>
+        <v>8.9999999999999858E-2</v>
+      </c>
+      <c r="H21">
         <v>82</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22">
         <v>19</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>1.74</v>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
+      <c r="D22" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22">
         <v>0</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>-1.6</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22">
+        <f t="shared" si="0"/>
+        <v>1.6</v>
+      </c>
+      <c r="H22">
         <v>82</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23">
         <v>19</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>1.74</v>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
+      <c r="D23" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23">
         <v>4.25</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>-3.21</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23">
+        <f t="shared" si="0"/>
+        <v>1.04</v>
+      </c>
+      <c r="H23">
         <v>82</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24">
         <v>19</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>1.74</v>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
+      <c r="D24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24">
         <v>-16</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>-17</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H24">
         <v>82</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>20</v>
-      </c>
-      <c r="B25" t="n">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>20</v>
+      </c>
+      <c r="B25">
         <v>1.64</v>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Feminine</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
+      <c r="D25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25">
         <v>-12.5</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>-13.26</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25">
+        <f t="shared" si="0"/>
+        <v>0.75999999999999979</v>
+      </c>
+      <c r="H25">
         <v>52</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>20</v>
-      </c>
-      <c r="B26" t="n">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>20</v>
+      </c>
+      <c r="B26">
         <v>1.64</v>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Feminine</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
+      <c r="D26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26">
         <v>-15.8</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>-16.75</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26">
+        <f t="shared" si="0"/>
+        <v>0.94999999999999929</v>
+      </c>
+      <c r="H26">
         <v>52</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>20</v>
-      </c>
-      <c r="B27" t="n">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>20</v>
+      </c>
+      <c r="B27">
         <v>1.64</v>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Feminine</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
+      <c r="D27" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27">
         <v>-16</v>
       </c>
-      <c r="F27" t="n">
-        <v>-16.44</v>
-      </c>
-      <c r="G27" t="n">
+      <c r="F27">
+        <v>-16.440000000000001</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="0"/>
+        <v>0.44000000000000128</v>
+      </c>
+      <c r="H27">
         <v>52</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>20</v>
-      </c>
-      <c r="B28" t="n">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>20</v>
+      </c>
+      <c r="B28">
         <v>1.64</v>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Feminine</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
+      <c r="D28" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28">
         <v>-14.2</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28">
         <v>-15.01</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28">
+        <f t="shared" si="0"/>
+        <v>0.8100000000000005</v>
+      </c>
+      <c r="H28">
         <v>52</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>20</v>
-      </c>
-      <c r="B29" t="n">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>20</v>
+      </c>
+      <c r="B29">
         <v>1.64</v>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Feminine</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
+      <c r="D29" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29">
         <v>-9</v>
       </c>
-      <c r="F29" t="n">
-        <v>-9.380000000000001</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="F29">
+        <v>-9.3800000000000008</v>
+      </c>
+      <c r="G29">
+        <f t="shared" si="0"/>
+        <v>0.38000000000000078</v>
+      </c>
+      <c r="H29">
         <v>52</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>20</v>
-      </c>
-      <c r="B30" t="n">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>20</v>
+      </c>
+      <c r="B30">
         <v>1.64</v>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Feminine</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
+      <c r="D30" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30">
         <v>0</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30">
         <v>-1.84</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30">
+        <f t="shared" si="0"/>
+        <v>1.84</v>
+      </c>
+      <c r="H30">
         <v>52</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>20</v>
-      </c>
-      <c r="B31" t="n">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>20</v>
+      </c>
+      <c r="B31">
         <v>1.64</v>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Feminine</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
+      <c r="D31" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31">
         <v>-11</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31">
         <v>-11.47</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31">
+        <f t="shared" si="0"/>
+        <v>0.47000000000000064</v>
+      </c>
+      <c r="H31">
         <v>52</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Feminine</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>20</v>
+      </c>
+      <c r="B32">
+        <v>1.64</v>
+      </c>
+      <c r="D32" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32">
         <v>-7</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>-7.51</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+      <c r="F32">
+        <v>-7.51</v>
+      </c>
+      <c r="G32">
+        <f t="shared" si="0"/>
+        <v>0.50999999999999979</v>
+      </c>
+      <c r="H32">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>58</v>
+      </c>
+      <c r="B33">
+        <v>1.76</v>
+      </c>
+      <c r="D33" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33">
+        <v>-13.5</v>
+      </c>
+      <c r="F33">
+        <v>-12.83</v>
+      </c>
+      <c r="G33">
+        <f t="shared" si="0"/>
+        <v>0.66999999999999993</v>
+      </c>
+      <c r="H33">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>58</v>
+      </c>
+      <c r="B34">
+        <v>1.76</v>
+      </c>
+      <c r="D34" t="s">
+        <v>7</v>
+      </c>
+      <c r="E34">
+        <v>-11</v>
+      </c>
+      <c r="F34">
+        <v>-10.97</v>
+      </c>
+      <c r="G34">
+        <f t="shared" si="0"/>
+        <v>2.9999999999999361E-2</v>
+      </c>
+      <c r="H34">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>58</v>
+      </c>
+      <c r="B35">
+        <v>1.76</v>
+      </c>
+      <c r="D35" t="s">
+        <v>7</v>
+      </c>
+      <c r="E35">
+        <v>-10.5</v>
+      </c>
+      <c r="F35">
+        <v>-10.32</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="0"/>
+        <v>0.17999999999999972</v>
+      </c>
+      <c r="H35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>58</v>
+      </c>
+      <c r="B36">
+        <v>1.76</v>
+      </c>
+      <c r="D36" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36">
+        <v>-9.5</v>
+      </c>
+      <c r="F36">
+        <v>-7.33</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="0"/>
+        <v>2.17</v>
+      </c>
+      <c r="H36">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>58</v>
+      </c>
+      <c r="B37">
+        <v>1.76</v>
+      </c>
+      <c r="D37" t="s">
+        <v>7</v>
+      </c>
+      <c r="E37">
+        <v>-18</v>
+      </c>
+      <c r="F37">
+        <v>-17.54</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="0"/>
+        <v>0.46000000000000085</v>
+      </c>
+      <c r="H37">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>58</v>
+      </c>
+      <c r="B38">
+        <v>1.76</v>
+      </c>
+      <c r="D38" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38">
+        <v>-10</v>
+      </c>
+      <c r="F38">
+        <v>-9.25</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+      <c r="H38">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>58</v>
+      </c>
+      <c r="B39">
+        <v>1.76</v>
+      </c>
+      <c r="D39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39">
+        <v>-10</v>
+      </c>
+      <c r="F39">
+        <v>-10.41</v>
+      </c>
+      <c r="G39">
+        <f t="shared" si="0"/>
+        <v>0.41000000000000014</v>
+      </c>
+      <c r="H39">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>58</v>
+      </c>
+      <c r="B40">
+        <v>1.76</v>
+      </c>
+      <c r="D40" t="s">
+        <v>7</v>
+      </c>
+      <c r="E40">
+        <v>-7</v>
+      </c>
+      <c r="F40" t="s">
+        <v>9</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="0"/>
+        <v>0.59999999999999964</v>
+      </c>
+      <c r="H40">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
